--- a/engine/scem_study/SCEM_Valuation_Model_04092026_public.xlsx
+++ b/engine/scem_study/SCEM_Valuation_Model_04092026_public.xlsx
@@ -72,13 +72,13 @@
       <color rgb="000000FF"/>
     </font>
     <font>
-      <b val="1"/>
+      <color rgb="00008000"/>
+    </font>
+    <font>
       <color rgb="00000000"/>
     </font>
     <font>
-      <color rgb="00008000"/>
-    </font>
-    <font>
+      <b val="1"/>
       <color rgb="00000000"/>
     </font>
     <font>
@@ -121,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -129,16 +129,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -148,26 +148,27 @@
     <xf numFmtId="169" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="172" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -961,27 +962,27 @@
         <f>Assumptions!$B$97</f>
         <v/>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <f>C5</f>
         <v/>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <f>D5+DCF!B12-DCF!B8</f>
         <v/>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <f>E5+DCF!C12-DCF!C8</f>
         <v/>
       </c>
-      <c r="G5" s="30">
+      <c r="G5" s="31">
         <f>F5+DCF!D12-DCF!D8</f>
         <v/>
       </c>
-      <c r="H5" s="30">
+      <c r="H5" s="31">
         <f>G5+DCF!E12-DCF!E8</f>
         <v/>
       </c>
-      <c r="I5" s="30">
+      <c r="I5" s="31">
         <f>H5+DCF!F12-DCF!F8</f>
         <v/>
       </c>
@@ -998,27 +999,27 @@
       <c r="C6" s="23" t="n">
         <v>900</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <f>C6</f>
         <v/>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <f>D6+DCF!B13</f>
         <v/>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <f>E6+DCF!C13</f>
         <v/>
       </c>
-      <c r="G6" s="30">
+      <c r="G6" s="31">
         <f>F6+DCF!D13</f>
         <v/>
       </c>
-      <c r="H6" s="30">
+      <c r="H6" s="31">
         <f>G6+DCF!E13</f>
         <v/>
       </c>
-      <c r="I6" s="30">
+      <c r="I6" s="31">
         <f>H6+DCF!F13</f>
         <v/>
       </c>
@@ -1032,7 +1033,7 @@
       <c r="B7" s="23" t="n">
         <v>1333.45762648</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <f>Assumptions!$B$59/1.25</f>
         <v/>
       </c>
@@ -1040,23 +1041,23 @@
         <f>Assumptions!$B$59</f>
         <v/>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <f>D7+'Cash Flow'!E14</f>
         <v/>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <f>E7+'Cash Flow'!F14</f>
         <v/>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="31">
         <f>F7+'Cash Flow'!G14</f>
         <v/>
       </c>
-      <c r="H7" s="30">
+      <c r="H7" s="31">
         <f>G7+'Cash Flow'!H14</f>
         <v/>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="31">
         <f>H7+'Cash Flow'!I14</f>
         <v/>
       </c>
@@ -1067,35 +1068,35 @@
           <t>Total assets (condensed)</t>
         </is>
       </c>
-      <c r="B8" s="31">
+      <c r="B8" s="32">
         <f>SUM(B5:B7)</f>
         <v/>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="27">
         <f>Assumptions!$B$69</f>
         <v/>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="32">
         <f>SUM(D5:D7)</f>
         <v/>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="32">
         <f>SUM(E5:E7)</f>
         <v/>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="32">
         <f>SUM(F5:F7)</f>
         <v/>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="32">
         <f>SUM(G5:G7)</f>
         <v/>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="32">
         <f>SUM(H5:H7)</f>
         <v/>
       </c>
-      <c r="I8" s="31">
+      <c r="I8" s="32">
         <f>SUM(I5:I7)</f>
         <v/>
       </c>
@@ -1106,35 +1107,35 @@
           <t>Gross debt</t>
         </is>
       </c>
-      <c r="B9" s="33">
+      <c r="B9" s="34">
         <f>Assumptions!$B$50</f>
         <v/>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="34">
         <f>Assumptions!$B$50</f>
         <v/>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="34">
         <f>Assumptions!$B$50</f>
         <v/>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="34">
         <f>Assumptions!$B$50</f>
         <v/>
       </c>
-      <c r="F9" s="33">
+      <c r="F9" s="34">
         <f>Assumptions!$B$50</f>
         <v/>
       </c>
-      <c r="G9" s="33">
+      <c r="G9" s="34">
         <f>Assumptions!$B$50</f>
         <v/>
       </c>
-      <c r="H9" s="33">
+      <c r="H9" s="34">
         <f>Assumptions!$B$50</f>
         <v/>
       </c>
-      <c r="I9" s="33">
+      <c r="I9" s="34">
         <f>Assumptions!$B$50</f>
         <v/>
       </c>
@@ -1145,35 +1146,35 @@
           <t>Other liabilities</t>
         </is>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="31">
         <f>B11-B9</f>
         <v/>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <f>C11-C9</f>
         <v/>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <f>D11-D9</f>
         <v/>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <f>E11-E9</f>
         <v/>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <f>F11-F9</f>
         <v/>
       </c>
-      <c r="G10" s="30">
+      <c r="G10" s="31">
         <f>G11-G9</f>
         <v/>
       </c>
-      <c r="H10" s="30">
+      <c r="H10" s="31">
         <f>H11-H9</f>
         <v/>
       </c>
-      <c r="I10" s="30">
+      <c r="I10" s="31">
         <f>I11-I9</f>
         <v/>
       </c>
@@ -1184,7 +1185,7 @@
           <t>Total liabilities</t>
         </is>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="31">
         <f>B8-B12</f>
         <v/>
       </c>
@@ -1192,27 +1193,27 @@
         <f>Assumptions!$B$70</f>
         <v/>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <f>D8-D12</f>
         <v/>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <f>E8-E12</f>
         <v/>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <f>F8-F12</f>
         <v/>
       </c>
-      <c r="G11" s="30">
+      <c r="G11" s="31">
         <f>G8-G12</f>
         <v/>
       </c>
-      <c r="H11" s="30">
+      <c r="H11" s="31">
         <f>H8-H12</f>
         <v/>
       </c>
-      <c r="I11" s="30">
+      <c r="I11" s="31">
         <f>I8-I12</f>
         <v/>
       </c>
@@ -1223,35 +1224,35 @@
           <t>Shareholders' equity</t>
         </is>
       </c>
-      <c r="B12" s="31">
+      <c r="B12" s="32">
         <f>C12-Assumptions!$B$66</f>
         <v/>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="32">
         <f>C8-C11</f>
         <v/>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="27">
         <f>Assumptions!$B$60</f>
         <v/>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="32">
         <f>D12+'Income Statement'!E14-'Cash Flow'!E13</f>
         <v/>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="32">
         <f>E12+'Income Statement'!F14-'Cash Flow'!F13</f>
         <v/>
       </c>
-      <c r="G12" s="31">
+      <c r="G12" s="32">
         <f>F12+'Income Statement'!G14-'Cash Flow'!G13</f>
         <v/>
       </c>
-      <c r="H12" s="31">
+      <c r="H12" s="32">
         <f>G12+'Income Statement'!H14-'Cash Flow'!H13</f>
         <v/>
       </c>
-      <c r="I12" s="31">
+      <c r="I12" s="32">
         <f>H12+'Income Statement'!I14-'Cash Flow'!I13</f>
         <v/>
       </c>
@@ -1262,7 +1263,7 @@
           <t>Equity — reported cross-check</t>
         </is>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <f>C12+Assumptions!$B$67</f>
         <v/>
       </c>
@@ -1273,35 +1274,35 @@
           <t>Net cash</t>
         </is>
       </c>
-      <c r="B14" s="30">
+      <c r="B14" s="31">
         <f>B7-B9</f>
         <v/>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="31">
         <f>C7-C9</f>
         <v/>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="31">
         <f>D7-D9</f>
         <v/>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <f>E7-E9</f>
         <v/>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <f>F7-F9</f>
         <v/>
       </c>
-      <c r="G14" s="30">
+      <c r="G14" s="31">
         <f>G7-G9</f>
         <v/>
       </c>
-      <c r="H14" s="30">
+      <c r="H14" s="31">
         <f>H7-H9</f>
         <v/>
       </c>
-      <c r="I14" s="30">
+      <c r="I14" s="31">
         <f>I7-I9</f>
         <v/>
       </c>
@@ -1312,27 +1313,27 @@
           <t>Return on equity</t>
         </is>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="11">
         <f>Assumptions!$B$67/D12</f>
         <v/>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="11">
         <f>'Income Statement'!E14/E12</f>
         <v/>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="11">
         <f>'Income Statement'!F14/F12</f>
         <v/>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="11">
         <f>'Income Statement'!G14/G12</f>
         <v/>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="11">
         <f>'Income Statement'!H14/H12</f>
         <v/>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="11">
         <f>'Income Statement'!I14/I12</f>
         <v/>
       </c>
@@ -1489,23 +1490,23 @@
           <t>Less change in working capital</t>
         </is>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <f>-DCF!B13</f>
         <v/>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <f>-DCF!C13</f>
         <v/>
       </c>
-      <c r="G6" s="30">
+      <c r="G6" s="31">
         <f>-DCF!D13</f>
         <v/>
       </c>
-      <c r="H6" s="30">
+      <c r="H6" s="31">
         <f>-DCF!E13</f>
         <v/>
       </c>
-      <c r="I6" s="30">
+      <c r="I6" s="31">
         <f>-DCF!F13</f>
         <v/>
       </c>
@@ -1516,23 +1517,23 @@
           <t>Less capital expenditure</t>
         </is>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <f>-DCF!B12</f>
         <v/>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <f>-DCF!C12</f>
         <v/>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="31">
         <f>-DCF!D12</f>
         <v/>
       </c>
-      <c r="H7" s="30">
+      <c r="H7" s="31">
         <f>-DCF!E12</f>
         <v/>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="31">
         <f>-DCF!F12</f>
         <v/>
       </c>
@@ -1543,23 +1544,23 @@
           <t>Operating free cash flow</t>
         </is>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="32">
         <f>SUM(E5:E7)</f>
         <v/>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="32">
         <f>SUM(F5:F7)</f>
         <v/>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="32">
         <f>SUM(G5:G7)</f>
         <v/>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="32">
         <f>SUM(H5:H7)</f>
         <v/>
       </c>
-      <c r="I8" s="31">
+      <c r="I8" s="32">
         <f>SUM(I5:I7)</f>
         <v/>
       </c>
@@ -1597,23 +1598,23 @@
           <t>Less net reinvestment (growth at terminal ROIC)</t>
         </is>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <f>-DCF!B14</f>
         <v/>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <f>-DCF!C14</f>
         <v/>
       </c>
-      <c r="G10" s="30">
+      <c r="G10" s="31">
         <f>-DCF!D14</f>
         <v/>
       </c>
-      <c r="H10" s="30">
+      <c r="H10" s="31">
         <f>-DCF!E14</f>
         <v/>
       </c>
-      <c r="I10" s="30">
+      <c r="I10" s="31">
         <f>-DCF!F14</f>
         <v/>
       </c>
@@ -1624,23 +1625,23 @@
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="32">
         <f>DCF!B15</f>
         <v/>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="32">
         <f>DCF!C15</f>
         <v/>
       </c>
-      <c r="G11" s="31">
+      <c r="G11" s="32">
         <f>DCF!D15</f>
         <v/>
       </c>
-      <c r="H11" s="31">
+      <c r="H11" s="32">
         <f>DCF!E15</f>
         <v/>
       </c>
-      <c r="I11" s="31">
+      <c r="I11" s="32">
         <f>DCF!F15</f>
         <v/>
       </c>
@@ -1651,23 +1652,23 @@
           <t>Treasury income after tax</t>
         </is>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <f>'Income Statement'!E10*(1-Assumptions!$B$7)</f>
         <v/>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <f>'Income Statement'!F10*(1-Assumptions!$B$7)</f>
         <v/>
       </c>
-      <c r="G12" s="30">
+      <c r="G12" s="31">
         <f>'Income Statement'!G10*(1-Assumptions!$B$7)</f>
         <v/>
       </c>
-      <c r="H12" s="30">
+      <c r="H12" s="31">
         <f>'Income Statement'!H10*(1-Assumptions!$B$7)</f>
         <v/>
       </c>
-      <c r="I12" s="30">
+      <c r="I12" s="31">
         <f>'Income Statement'!I10*(1-Assumptions!$B$7)</f>
         <v/>
       </c>
@@ -1678,23 +1679,23 @@
           <t>Dividends paid</t>
         </is>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <f>'Income Statement'!E14*Assumptions!$B$41</f>
         <v/>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <f>'Income Statement'!F14*Assumptions!$B$41</f>
         <v/>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="31">
         <f>'Income Statement'!G14*Assumptions!$B$41</f>
         <v/>
       </c>
-      <c r="H13" s="30">
+      <c r="H13" s="31">
         <f>'Income Statement'!H14*Assumptions!$B$41</f>
         <v/>
       </c>
-      <c r="I13" s="30">
+      <c r="I13" s="31">
         <f>'Income Statement'!I14*Assumptions!$B$41</f>
         <v/>
       </c>
@@ -1705,23 +1706,23 @@
           <t>Net change in cash</t>
         </is>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="32">
         <f>'Income Statement'!E14+DCF!B8-DCF!B12-DCF!B13-E13</f>
         <v/>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="32">
         <f>'Income Statement'!F14+DCF!C8-DCF!C12-DCF!C13-F13</f>
         <v/>
       </c>
-      <c r="G14" s="31">
+      <c r="G14" s="32">
         <f>'Income Statement'!G14+DCF!D8-DCF!D12-DCF!D13-G13</f>
         <v/>
       </c>
-      <c r="H14" s="31">
+      <c r="H14" s="32">
         <f>'Income Statement'!H14+DCF!E8-DCF!E12-DCF!E13-H13</f>
         <v/>
       </c>
-      <c r="I14" s="31">
+      <c r="I14" s="32">
         <f>'Income Statement'!I14+DCF!F8-DCF!F12-DCF!F13-I13</f>
         <v/>
       </c>
@@ -2006,27 +2007,27 @@
           <t>Sales volume (Mt)</t>
         </is>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="29">
         <f>'Unit Build'!B10</f>
         <v/>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="29">
         <f>'Unit Build'!C10</f>
         <v/>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="29">
         <f>'Unit Build'!D10</f>
         <v/>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="29">
         <f>'Unit Build'!E10</f>
         <v/>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="29">
         <f>'Unit Build'!F10</f>
         <v/>
       </c>
-      <c r="I9" s="28">
+      <c r="I9" s="29">
         <f>'Unit Build'!G10</f>
         <v/>
       </c>
@@ -2068,27 +2069,27 @@
           <t>Kiln utilisation</t>
         </is>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="12">
         <f>'Unit Build'!B6</f>
         <v/>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="12">
         <f>'Unit Build'!C6</f>
         <v/>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="12">
         <f>'Unit Build'!D6</f>
         <v/>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="12">
         <f>'Unit Build'!E6</f>
         <v/>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="12">
         <f>'Unit Build'!F6</f>
         <v/>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="12">
         <f>'Unit Build'!G6</f>
         <v/>
       </c>
@@ -2099,35 +2100,35 @@
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="11">
         <f>B6/B5</f>
         <v/>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="11">
         <f>C6/C5</f>
         <v/>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="11">
         <f>D6/D5</f>
         <v/>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="11">
         <f>E6/E5</f>
         <v/>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="11">
         <f>F6/F5</f>
         <v/>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="11">
         <f>G6/G5</f>
         <v/>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="11">
         <f>H6/H5</f>
         <v/>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="11">
         <f>I6/I5</f>
         <v/>
       </c>
@@ -2138,31 +2139,31 @@
           <t>Revenue growth</t>
         </is>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="11">
         <f>C5/B5-1</f>
         <v/>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="11">
         <f>D5/C5-1</f>
         <v/>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="11">
         <f>E5/D5-1</f>
         <v/>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="11">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="11">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="11">
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="11">
         <f>I5/H5-1</f>
         <v/>
       </c>
@@ -2263,7 +2264,7 @@
       <c r="B5" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="C5" s="40" t="inlineStr">
+      <c r="C5" s="41" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
@@ -2293,7 +2294,7 @@
       <c r="B6" s="23" t="n">
         <v>62</v>
       </c>
-      <c r="C6" s="40" t="inlineStr">
+      <c r="C6" s="41" t="inlineStr">
         <is>
           <t>2026-11-08</t>
         </is>
@@ -2401,84 +2402,84 @@
       <c r="H12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="41" t="inlineStr">
+      <c r="A13" s="42" t="inlineStr">
         <is>
           <t>Market panel verdict (Egypt)</t>
         </is>
       </c>
-      <c r="B13" s="42" t="inlineStr">
+      <c r="B13" s="43" t="inlineStr">
         <is>
           <t>PASS — skill +0.0158, 90% interval [0.009, 0.022]</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="41" t="inlineStr">
+      <c r="A14" s="42" t="inlineStr">
         <is>
           <t>This name's verdict</t>
         </is>
       </c>
-      <c r="B14" s="42" t="inlineStr">
+      <c r="B14" s="43" t="inlineStr">
         <is>
           <t>PARITY at every bootstrap block size {2,3,4}</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="41" t="inlineStr">
+      <c r="A15" s="42" t="inlineStr">
         <is>
           <t>This name's CRPS skill vs a random walk</t>
         </is>
       </c>
-      <c r="B15" s="42" t="inlineStr">
+      <c r="B15" s="43" t="inlineStr">
         <is>
           <t>-0.1276 — BELOW zero</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="41" t="inlineStr">
+      <c r="A16" s="42" t="inlineStr">
         <is>
           <t>Coverage 50 / 80 / 90</t>
         </is>
       </c>
-      <c r="B16" s="42" t="inlineStr">
+      <c r="B16" s="43" t="inlineStr">
         <is>
           <t>0.76 / 0.82 / 0.94 against nominal 0.50 / 0.80 / 0.90 — OVER-COVERED</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="41" t="inlineStr">
+      <c r="A17" s="42" t="inlineStr">
         <is>
           <t>Cone width versus the benchmark</t>
         </is>
       </c>
-      <c r="B17" s="42" t="inlineStr">
+      <c r="B17" s="43" t="inlineStr">
         <is>
           <t>4.71x</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="41" t="inlineStr">
+      <c r="A18" s="42" t="inlineStr">
         <is>
           <t>Why</t>
         </is>
       </c>
-      <c r="B18" s="42" t="inlineStr">
+      <c r="B18" s="43" t="inlineStr">
         <is>
           <t>SCEM prints an unchanged close on 29.3% of sessions, 3.4x the Egyptian panel median and 2nd thinnest of 33 names. On such a series the benchmark's own volatility estimate collapses in quiet quarters.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="41" t="inlineStr">
+      <c r="A19" s="42" t="inlineStr">
         <is>
           <t>Consequence</t>
         </is>
       </c>
-      <c r="B19" s="42" t="inlineStr">
+      <c r="B19" s="43" t="inlineStr">
         <is>
           <t>The map is ILLUSTRATIVE ONLY. It is materially too wide and must not be read with the confidence of a calibrated name.</t>
         </is>
@@ -2539,7 +2540,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="41" t="inlineStr">
+      <c r="A4" s="42" t="inlineStr">
         <is>
           <t>Explicit WACC (rows) × terminal growth (columns) — fair value per share (EGP)</t>
         </is>
@@ -2575,106 +2576,106 @@
     </row>
     <row r="6">
       <c r="A6" s="24" t="n">
-        <v>0.2525913769174497</v>
+        <v>0.2595969690413578</v>
       </c>
       <c r="B6" s="18" t="n">
-        <v>85.43422679150203</v>
+        <v>105.7744753435361</v>
       </c>
       <c r="C6" s="18" t="n">
-        <v>89.35597090426347</v>
+        <v>109.9344802635012</v>
       </c>
       <c r="D6" s="18" t="n">
-        <v>93.81299327661097</v>
+        <v>114.7002382683086</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>98.92976661953224</v>
+        <v>120.2117224397915</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>104.8721778078644</v>
+        <v>126.65563005976</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="24" t="n">
-        <v>0.2675913769174497</v>
+        <v>0.2745969690413578</v>
       </c>
       <c r="B7" s="18" t="n">
-        <v>84.00762868477028</v>
+        <v>104.4517863458828</v>
       </c>
       <c r="C7" s="18" t="n">
-        <v>87.83159587372695</v>
+        <v>108.5339013273708</v>
       </c>
       <c r="D7" s="18" t="n">
-        <v>92.17717374217652</v>
+        <v>113.2104275632422</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>97.16566705137153</v>
+        <v>118.6187173464268</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>102.9587402831979</v>
+        <v>124.9419723283029</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="24" t="n">
-        <v>0.2825913769174497</v>
+        <v>0.2895969690413578</v>
       </c>
       <c r="B8" s="18" t="n">
-        <v>82.62809864313135</v>
+        <v>103.1622934599548</v>
       </c>
       <c r="C8" s="18" t="n">
-        <v>86.35757426555165</v>
+        <v>107.1685387943926</v>
       </c>
       <c r="D8" s="18" t="n">
-        <v>90.59545467134566</v>
+        <v>111.7581477345618</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>95.45998360748743</v>
+        <v>117.0659197619123</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>101.1087456946099</v>
+        <v>123.2716515662545</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="24" t="n">
-        <v>0.2975913769174497</v>
+        <v>0.3045969690413578</v>
       </c>
       <c r="B9" s="18" t="n">
-        <v>81.29365747766214</v>
+        <v>101.9048910689767</v>
       </c>
       <c r="C9" s="18" t="n">
-        <v>84.93178753792651</v>
+        <v>105.8372188335528</v>
       </c>
       <c r="D9" s="18" t="n">
-        <v>89.0655585408756</v>
+        <v>110.3421468040977</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>93.81025560970393</v>
+        <v>115.5519873327781</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>99.31951997756768</v>
+        <v>121.6432197553057</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="24" t="n">
-        <v>0.3125913769174498</v>
+        <v>0.3195969690413578</v>
       </c>
       <c r="B10" s="18" t="n">
-        <v>80.00242746957701</v>
+        <v>100.6785198127876</v>
       </c>
       <c r="C10" s="18" t="n">
-        <v>83.55222579774555</v>
+        <v>104.5388167423198</v>
       </c>
       <c r="D10" s="18" t="n">
-        <v>87.58532466717638</v>
+        <v>108.9612252122133</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>92.21414865720189</v>
+        <v>114.075633928951</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>97.58852634175473</v>
+        <v>120.0552895491089</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="41" t="inlineStr">
+      <c r="A12" s="42" t="inlineStr">
         <is>
           <t>NET CASH — the largest single uncertainty, now sensitised</t>
         </is>
@@ -2684,50 +2685,50 @@
       <c r="A13" s="6" t="inlineStr"/>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>5,033</t>
+          <t>5,055</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>5,783</t>
+          <t>5,805</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>6,533</t>
+          <t>6,555</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>7,283</t>
+          <t>7,305</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>8,033</t>
+          <t>8,055</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="43" t="inlineStr">
+      <c r="A14" s="44" t="inlineStr">
         <is>
           <t>Fair value per share (EGP)</t>
         </is>
       </c>
       <c r="B14" s="18" t="n">
-        <v>84.84419607645873</v>
+        <v>117.5203929713675</v>
       </c>
       <c r="C14" s="18" t="n">
-        <v>87.7198253739022</v>
+        <v>120.396022268811</v>
       </c>
       <c r="D14" s="18" t="n">
-        <v>90.59545467134566</v>
+        <v>123.2716515662545</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>93.47108396878912</v>
+        <v>126.1472808636979</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>96.34671326623258</v>
+        <v>129.0229101611414</v>
       </c>
     </row>
     <row r="16">
@@ -2745,7 +2746,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="41" t="inlineStr">
+      <c r="A20" s="42" t="inlineStr">
         <is>
           <t>Beta — fair value per share (EGP)</t>
         </is>
@@ -2780,29 +2781,29 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="43" t="inlineStr">
+      <c r="A22" s="44" t="inlineStr">
         <is>
           <t>Fair value</t>
         </is>
       </c>
       <c r="B22" s="18" t="n">
-        <v>109.4877914735178</v>
+        <v>152.6200660812137</v>
       </c>
       <c r="C22" s="18" t="n">
-        <v>98.99877527851166</v>
+        <v>136.0802085964604</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>97.30640473659925</v>
+        <v>133.4702009329797</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>90.59545467134566</v>
+        <v>123.2716515662545</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>80.74732742837557</v>
+        <v>108.7151473219916</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="41" t="inlineStr">
+      <c r="A24" s="42" t="inlineStr">
         <is>
           <t>EBITDA margin shift — fair value per share (EGP)</t>
         </is>
@@ -2837,25 +2838,25 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="43" t="inlineStr">
+      <c r="A26" s="44" t="inlineStr">
         <is>
           <t>Fair value</t>
         </is>
       </c>
       <c r="B26" s="18" t="n">
-        <v>82.80602149093339</v>
+        <v>110.8208758124425</v>
       </c>
       <c r="C26" s="18" t="n">
-        <v>86.63401685311617</v>
+        <v>117.0462636893485</v>
       </c>
       <c r="D26" s="18" t="n">
-        <v>90.59545467134566</v>
+        <v>123.2716515662545</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>94.67036103810479</v>
+        <v>129.4970394431604</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>98.84255891259662</v>
+        <v>135.7224273200664</v>
       </c>
     </row>
     <row r="28">
@@ -3155,35 +3156,35 @@
           <t>Return on equity</t>
         </is>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="11">
         <f>'Income Statement'!B14/'Balance Sheet'!B12</f>
         <v/>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="11">
         <f>'Income Statement'!C14/'Balance Sheet'!C12</f>
         <v/>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <f>'Income Statement'!D14/'Balance Sheet'!D12</f>
         <v/>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="11">
         <f>'Income Statement'!E14/'Balance Sheet'!E12</f>
         <v/>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="11">
         <f>'Income Statement'!F14/'Balance Sheet'!F12</f>
         <v/>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="11">
         <f>'Income Statement'!G14/'Balance Sheet'!G12</f>
         <v/>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="11">
         <f>'Income Statement'!H14/'Balance Sheet'!H12</f>
         <v/>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="11">
         <f>'Income Statement'!I14/'Balance Sheet'!I12</f>
         <v/>
       </c>
@@ -3194,27 +3195,27 @@
           <t>EBITDA per tonne sold (EGP)</t>
         </is>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <f>'Income Statement'!D6/'Summary Financials'!D9</f>
         <v/>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <f>'Income Statement'!E6/'Summary Financials'!E9</f>
         <v/>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <f>'Income Statement'!F6/'Summary Financials'!F9</f>
         <v/>
       </c>
-      <c r="G11" s="30">
+      <c r="G11" s="31">
         <f>'Income Statement'!G6/'Summary Financials'!G9</f>
         <v/>
       </c>
-      <c r="H11" s="30">
+      <c r="H11" s="31">
         <f>'Income Statement'!H6/'Summary Financials'!H9</f>
         <v/>
       </c>
-      <c r="I11" s="30">
+      <c r="I11" s="31">
         <f>'Income Statement'!I6/'Summary Financials'!I9</f>
         <v/>
       </c>
@@ -3225,35 +3226,35 @@
           <t>Price / earnings (at spot)</t>
         </is>
       </c>
-      <c r="B12" s="32">
+      <c r="B12" s="33">
         <f>Assumptions!$B$5/B5</f>
         <v/>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="33">
         <f>Assumptions!$B$5/C5</f>
         <v/>
       </c>
-      <c r="D12" s="32">
+      <c r="D12" s="33">
         <f>Assumptions!$B$5/D5</f>
         <v/>
       </c>
-      <c r="E12" s="32">
+      <c r="E12" s="33">
         <f>Assumptions!$B$5/E5</f>
         <v/>
       </c>
-      <c r="F12" s="32">
+      <c r="F12" s="33">
         <f>Assumptions!$B$5/F5</f>
         <v/>
       </c>
-      <c r="G12" s="32">
+      <c r="G12" s="33">
         <f>Assumptions!$B$5/G5</f>
         <v/>
       </c>
-      <c r="H12" s="32">
+      <c r="H12" s="33">
         <f>Assumptions!$B$5/H5</f>
         <v/>
       </c>
-      <c r="I12" s="32">
+      <c r="I12" s="33">
         <f>Assumptions!$B$5/I5</f>
         <v/>
       </c>
@@ -3264,35 +3265,35 @@
           <t>EV / EBITDA (at spot)</t>
         </is>
       </c>
-      <c r="B13" s="32">
+      <c r="B13" s="33">
         <f>(Assumptions!$B$5*Assumptions!$B$6-('Balance Sheet'!B7-'Balance Sheet'!B9))/'Income Statement'!B6</f>
         <v/>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="33">
         <f>(Assumptions!$B$5*Assumptions!$B$6-('Balance Sheet'!C7-'Balance Sheet'!C9))/'Income Statement'!C6</f>
         <v/>
       </c>
-      <c r="D13" s="32">
+      <c r="D13" s="33">
         <f>(Assumptions!$B$5*Assumptions!$B$6-('Balance Sheet'!D7-'Balance Sheet'!D9))/'Income Statement'!D6</f>
         <v/>
       </c>
-      <c r="E13" s="32">
+      <c r="E13" s="33">
         <f>(Assumptions!$B$5*Assumptions!$B$6-('Balance Sheet'!E7-'Balance Sheet'!E9))/'Income Statement'!E6</f>
         <v/>
       </c>
-      <c r="F13" s="32">
+      <c r="F13" s="33">
         <f>(Assumptions!$B$5*Assumptions!$B$6-('Balance Sheet'!F7-'Balance Sheet'!F9))/'Income Statement'!F6</f>
         <v/>
       </c>
-      <c r="G13" s="32">
+      <c r="G13" s="33">
         <f>(Assumptions!$B$5*Assumptions!$B$6-('Balance Sheet'!G7-'Balance Sheet'!G9))/'Income Statement'!G6</f>
         <v/>
       </c>
-      <c r="H13" s="32">
+      <c r="H13" s="33">
         <f>(Assumptions!$B$5*Assumptions!$B$6-('Balance Sheet'!H7-'Balance Sheet'!H9))/'Income Statement'!H6</f>
         <v/>
       </c>
-      <c r="I13" s="32">
+      <c r="I13" s="33">
         <f>(Assumptions!$B$5*Assumptions!$B$6-('Balance Sheet'!I7-'Balance Sheet'!I9))/'Income Statement'!I6</f>
         <v/>
       </c>
@@ -3499,7 +3500,7 @@
           <t>SCEM capacity as % of Egyptian capacity</t>
         </is>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="11">
         <f>Assumptions!$B$12/B14</f>
         <v/>
       </c>
@@ -3510,7 +3511,7 @@
           <t>Revival capacity as % of domestic consumption</t>
         </is>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="11">
         <f>B18/B15</f>
         <v/>
       </c>
@@ -3521,7 +3522,7 @@
           <t>Structural surplus (capacity less consumption, Mt)</t>
         </is>
       </c>
-      <c r="B21" s="33">
+      <c r="B21" s="34">
         <f>B14-B15</f>
         <v/>
       </c>
@@ -3532,7 +3533,7 @@
           <t>SCEM EV/EBITDA at spot on FY2026E</t>
         </is>
       </c>
-      <c r="B22" s="32">
+      <c r="B22" s="33">
         <f>'Per-Share &amp; Ratios'!E13</f>
         <v/>
       </c>
@@ -3682,12 +3683,12 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
           <t>Value per share (EGP)</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Weight</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -3707,19 +3708,20 @@
           <t>DCF (cash flow)</t>
         </is>
       </c>
-      <c r="B13" s="7">
-        <f>'Fundamental Valuation'!B5</f>
-        <v/>
-      </c>
-      <c r="C13" s="11">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PRIMARY — this IS the central</t>
+        </is>
+      </c>
+      <c r="C13" s="7">
         <f>'Fundamental Valuation'!C5</f>
         <v/>
       </c>
-      <c r="D13" s="12">
-        <f>B13/$B$5-1</f>
-        <v/>
-      </c>
-      <c r="E13" s="11">
+      <c r="D13" s="11">
+        <f>C13/$B$5-1</f>
+        <v/>
+      </c>
+      <c r="E13" s="12">
         <f>DCF!B33</f>
         <v/>
       </c>
@@ -3730,84 +3732,87 @@
           <t>Relative multiples</t>
         </is>
       </c>
-      <c r="B14" s="7">
-        <f>'Fundamental Valuation'!B6</f>
-        <v/>
-      </c>
-      <c r="C14" s="11">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>cross-check</t>
+        </is>
+      </c>
+      <c r="C14" s="7">
         <f>'Fundamental Valuation'!C6</f>
         <v/>
       </c>
-      <c r="D14" s="12">
-        <f>B14/$B$5-1</f>
+      <c r="D14" s="11">
+        <f>C14/$B$5-1</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Normalised earnings</t>
-        </is>
-      </c>
-      <c r="B15" s="7">
-        <f>'Fundamental Valuation'!B7</f>
-        <v/>
-      </c>
-      <c r="C15" s="11">
+          <t>Asset / replacement cost</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>cross-check</t>
+        </is>
+      </c>
+      <c r="C15" s="7">
         <f>'Fundamental Valuation'!C7</f>
         <v/>
       </c>
-      <c r="D15" s="12">
-        <f>B15/$B$5-1</f>
+      <c r="D15" s="11">
+        <f>C15/$B$5-1</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Asset / replacement cost</t>
-        </is>
-      </c>
-      <c r="B16" s="7">
-        <f>'Fundamental Valuation'!B8</f>
-        <v/>
-      </c>
-      <c r="C16" s="11">
+          <t>Book value (disclosed floor)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>disclosed floor — never weighted</t>
+        </is>
+      </c>
+      <c r="C16" s="7">
         <f>'Fundamental Valuation'!C8</f>
         <v/>
       </c>
-      <c r="D16" s="12">
-        <f>B16/$B$5-1</f>
+      <c r="D16" s="11">
+        <f>C16/$B$5-1</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Weighted central fair value (EGP)</t>
-        </is>
-      </c>
-      <c r="B17" s="13">
-        <f>'Fundamental Valuation'!D10</f>
+          <t>CENTRAL FAIR VALUE (EGP) — the primary lens, not a blend</t>
+        </is>
+      </c>
+      <c r="C17" s="13">
+        <f>'Fundamental Valuation'!C12</f>
         <v/>
       </c>
       <c r="D17" s="14">
-        <f>B17/$B$5-1</f>
+        <f>C17/$B$5-1</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Range across the four lenses (EGP)</t>
-        </is>
-      </c>
-      <c r="B18" s="15">
-        <f>MIN(B13:B16)</f>
-        <v/>
+          <t>Envelope — the primary with the EBITDA margin across its own filed span (EGP)</t>
+        </is>
       </c>
       <c r="C18" s="15">
-        <f>MAX(B13:B16)</f>
+        <f>'Fundamental Valuation'!C13</f>
+        <v/>
+      </c>
+      <c r="E18" s="15">
+        <f>'Fundamental Valuation'!C14</f>
         <v/>
       </c>
     </row>
@@ -3874,7 +3879,7 @@
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="12">
         <f>Assumptions!$B$55</f>
         <v/>
       </c>
@@ -3885,7 +3890,7 @@
           <t>Terminal return on invested capital (replacement basis)</t>
         </is>
       </c>
-      <c r="B26" s="11">
+      <c r="B26" s="12">
         <f>DCF!B24</f>
         <v/>
       </c>
@@ -3922,7 +3927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -3953,17 +3958,17 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
           <t>Value per share (EGP)</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Weight</t>
-        </is>
-      </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Weighted</t>
+          <t>vs spot</t>
         </is>
       </c>
     </row>
@@ -3973,16 +3978,17 @@
           <t>DCF (cash flow)</t>
         </is>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PRIMARY — this IS the central</t>
+        </is>
+      </c>
+      <c r="C5" s="7">
         <f>DCF!B39</f>
         <v/>
       </c>
-      <c r="C5" s="11">
-        <f>Assumptions!$B$87</f>
-        <v/>
-      </c>
-      <c r="D5" s="15">
-        <f>B5*C5</f>
+      <c r="D5" s="11">
+        <f>C5/$C$11-1</f>
         <v/>
       </c>
     </row>
@@ -3992,130 +3998,137 @@
           <t>Relative multiples</t>
         </is>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>cross-check</t>
+        </is>
+      </c>
+      <c r="C6" s="7">
         <f>'Relative &amp; Normalized'!B15</f>
         <v/>
       </c>
-      <c r="C6" s="11">
-        <f>Assumptions!$B$88</f>
-        <v/>
-      </c>
-      <c r="D6" s="15">
-        <f>B6*C6</f>
+      <c r="D6" s="11">
+        <f>C6/$C$11-1</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Normalised earnings</t>
-        </is>
-      </c>
-      <c r="B7" s="7">
-        <f>'Relative &amp; Normalized'!B26</f>
-        <v/>
-      </c>
-      <c r="C7" s="11">
-        <f>Assumptions!$B$89</f>
-        <v/>
-      </c>
-      <c r="D7" s="15">
-        <f>B7*C7</f>
+          <t>Asset / replacement cost</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>cross-check</t>
+        </is>
+      </c>
+      <c r="C7" s="7">
+        <f>'Relative &amp; Normalized'!B38</f>
+        <v/>
+      </c>
+      <c r="D7" s="11">
+        <f>C7/$C$11-1</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Asset / replacement cost</t>
-        </is>
-      </c>
-      <c r="B8" s="7">
-        <f>'Relative &amp; Normalized'!B38</f>
-        <v/>
-      </c>
-      <c r="C8" s="11">
-        <f>Assumptions!$B$90</f>
-        <v/>
-      </c>
-      <c r="D8" s="15">
-        <f>B8*C8</f>
+          <t>Book value (disclosed floor)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>disclosed floor — never weighted</t>
+        </is>
+      </c>
+      <c r="C8" s="7">
+        <f>'Relative &amp; Normalized'!B41</f>
+        <v/>
+      </c>
+      <c r="D8" s="11">
+        <f>C8/$C$11-1</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Weighted central fair value (EGP)</t>
-        </is>
-      </c>
-      <c r="D10" s="13">
-        <f>SUM(D5:D8)</f>
+          <t>RETIRED — normalised earnings power, not a lens for this class</t>
+        </is>
+      </c>
+      <c r="C10" s="15">
+        <f>'Relative &amp; Normalized'!B26</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Lowest lens</t>
-        </is>
-      </c>
-      <c r="B11" s="15">
-        <f>MIN(B5:B8)</f>
+          <t>Spot price (EGP)</t>
+        </is>
+      </c>
+      <c r="C11" s="7">
+        <f>Assumptions!$B$5</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Highest lens</t>
-        </is>
-      </c>
-      <c r="B12" s="15">
-        <f>MAX(B5:B8)</f>
+          <t>CENTRAL FAIR VALUE (EGP) — the primary lens, not a blend</t>
+        </is>
+      </c>
+      <c r="C12" s="13">
+        <f>C5</f>
+        <v/>
+      </c>
+      <c r="D12" s="14">
+        <f>C12/C11-1</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Median lens</t>
-        </is>
-      </c>
-      <c r="B13" s="15">
-        <f>MEDIAN(B5:B8)</f>
+          <t>Envelope, low — the primary with the EBITDA margin at its filed floor</t>
+        </is>
+      </c>
+      <c r="C13" s="7">
+        <f>Assumptions!$B$87</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Spot price (EGP)</t>
-        </is>
-      </c>
-      <c r="B14" s="7">
-        <f>Assumptions!$B$5</f>
+          <t>Envelope, high — the primary as published</t>
+        </is>
+      </c>
+      <c r="C14" s="15">
+        <f>C12</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Central versus spot</t>
-        </is>
-      </c>
-      <c r="B15" s="14">
-        <f>D10/B14-1</f>
+          <t>MEMO — what the retired four-lens blend would have read</t>
+        </is>
+      </c>
+      <c r="C15" s="7">
+        <f>Assumptions!$B$88</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Terminal value as % of enterprise value (DCF lens)</t>
-        </is>
-      </c>
-      <c r="B16" s="11">
+          <t>Terminal value as % of enterprise value (primary lens)</t>
+        </is>
+      </c>
+      <c r="C16" s="12">
         <f>DCF!B33</f>
         <v/>
       </c>
@@ -4123,20 +4136,28 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>The four lenses disagree by design — the spread between the cash-flow lens and the replacement-cost</t>
+          <t>The lenses disagree by design and the disagreement is PUBLISHED rather than averaged away. The</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>lens IS the question this company poses, and averaging it away would hide it.</t>
+          <t>cash-flow lens is the central for this class; the others are cross-checks read beside it, and the</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>book value is a disclosed floor that is never weighted into an answer.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A20:J20"/>
     <mergeCell ref="A19:J19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4149,7 +4170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I102"/>
+  <dimension ref="A1:I120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -4247,7 +4268,7 @@
         </is>
       </c>
       <c r="B9" s="21" t="n">
-        <v>49.8</v>
+        <v>50.25</v>
       </c>
     </row>
     <row r="11">
@@ -4568,19 +4589,19 @@
         <v>3503</v>
       </c>
       <c r="C30" s="23" t="n">
-        <v>3993.4</v>
+        <v>4063.48</v>
       </c>
       <c r="D30" s="23" t="n">
-        <v>4431.3</v>
+        <v>4551.0976</v>
       </c>
       <c r="E30" s="23" t="n">
-        <v>4781.6</v>
+        <v>4960.696384000001</v>
       </c>
       <c r="F30" s="23" t="n">
-        <v>5079.3</v>
+        <v>5332.748612800001</v>
       </c>
       <c r="G30" s="23" t="n">
-        <v>5359.6</v>
+        <v>5706.041015696001</v>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
@@ -4625,22 +4646,22 @@
         </is>
       </c>
       <c r="B32" s="21" t="n">
-        <v>49.8</v>
+        <v>50.25</v>
       </c>
       <c r="C32" s="21" t="n">
-        <v>55.39</v>
+        <v>55.11414634146342</v>
       </c>
       <c r="D32" s="21" t="n">
-        <v>59.96</v>
+        <v>60.22228673408688</v>
       </c>
       <c r="E32" s="21" t="n">
-        <v>63.12</v>
+        <v>64.04126101478509</v>
       </c>
       <c r="F32" s="21" t="n">
-        <v>65.42</v>
+        <v>67.16522496672583</v>
       </c>
       <c r="G32" s="21" t="n">
-        <v>67.34999999999999</v>
+        <v>70.11394216038698</v>
       </c>
     </row>
     <row r="33">
@@ -4653,19 +4674,19 @@
         <v>1</v>
       </c>
       <c r="C33" s="22" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="D33" s="22" t="n">
-        <v>1.265</v>
+        <v>1.2992</v>
       </c>
       <c r="E33" s="22" t="n">
-        <v>1.365</v>
+        <v>1.416128</v>
       </c>
       <c r="F33" s="22" t="n">
-        <v>1.45</v>
+        <v>1.5223376</v>
       </c>
       <c r="G33" s="22" t="n">
-        <v>1.53</v>
+        <v>1.628901232</v>
       </c>
     </row>
     <row r="35">
@@ -4690,19 +4711,19 @@
         </is>
       </c>
       <c r="B38" s="20" t="n">
-        <v>0.215</v>
+        <v>0.25</v>
       </c>
       <c r="C38" s="20" t="n">
-        <v>0.195</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="D38" s="20" t="n">
-        <v>0.18</v>
+        <v>0.1857142857142857</v>
       </c>
       <c r="E38" s="20" t="n">
-        <v>0.168</v>
+        <v>0.1642857142857143</v>
       </c>
       <c r="F38" s="20" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="39">
@@ -4769,7 +4790,7 @@
         </is>
       </c>
       <c r="B45" s="24" t="n">
-        <v>0.2231</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="46">
@@ -4809,7 +4830,7 @@
         </is>
       </c>
       <c r="B49" s="24" t="n">
-        <v>0.215</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="50">
@@ -4874,7 +4895,7 @@
         </is>
       </c>
       <c r="B55" s="20" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="56">
@@ -5170,52 +5191,36 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Weight — cash flow</t>
-        </is>
-      </c>
-      <c r="B87" s="20" t="n">
-        <v>0.48</v>
+          <t>Envelope floor — the primary at the filed margin floor</t>
+        </is>
+      </c>
+      <c r="B87" s="18" t="n">
+        <v>23.62014366636873</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Weight — relative</t>
-        </is>
-      </c>
-      <c r="B88" s="20" t="n">
-        <v>0.21</v>
+          <t>MEMO — the retired four-lens blend</t>
+        </is>
+      </c>
+      <c r="B88" s="18" t="n">
+        <v>95.96108438513127</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Weight — normalised</t>
-        </is>
-      </c>
-      <c r="B89" s="20" t="n">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Weight — asset</t>
-        </is>
-      </c>
-      <c r="B90" s="20" t="n">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Total (must be 100%)</t>
-        </is>
-      </c>
-      <c r="B91" s="14">
-        <f>SUM(B87:B90)</f>
-        <v/>
+          <t>Maintenance at current cost (replacement base / disclosed life)</t>
+        </is>
+      </c>
+      <c r="B89" s="23" t="n">
+        <v>958.8325110000001</v>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Replacement capital over the note 3/2 life — the SAME charge the terminal makes</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -5315,6 +5320,156 @@
       <c r="I102" s="5" t="inlineStr">
         <is>
           <t>EGP mn, FY2023-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Capital-charge convergence weight, FY2026</t>
+        </is>
+      </c>
+      <c r="B105" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>the share of the way from the company's own spend to current-cost maintenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Capital-charge convergence weight, FY2027</t>
+        </is>
+      </c>
+      <c r="B106" s="20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>the share of the way from the company's own spend to current-cost maintenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Capital-charge convergence weight, FY2028</t>
+        </is>
+      </c>
+      <c r="B107" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>the share of the way from the company's own spend to current-cost maintenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Capital-charge convergence weight, FY2029</t>
+        </is>
+      </c>
+      <c r="B108" s="20" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>the share of the way from the company's own spend to current-cost maintenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Capital-charge convergence weight, FY2030</t>
+        </is>
+      </c>
+      <c r="B109" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>the share of the way from the company's own spend to current-cost maintenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Cost-of-capital glide fraction, FY2026</t>
+        </is>
+      </c>
+      <c r="B116" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>the central bank's own easing calendar: the policy path's cumulative progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Cost-of-capital glide fraction, FY2027</t>
+        </is>
+      </c>
+      <c r="B117" s="26" t="n">
+        <v>0.357142857142857</v>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>the central bank's own easing calendar: the policy path's cumulative progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Cost-of-capital glide fraction, FY2028</t>
+        </is>
+      </c>
+      <c r="B118" s="26" t="n">
+        <v>0.642857142857143</v>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>the central bank's own easing calendar: the policy path's cumulative progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Cost-of-capital glide fraction, FY2029</t>
+        </is>
+      </c>
+      <c r="B119" s="26" t="n">
+        <v>0.857142857142857</v>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>the central bank's own easing calendar: the policy path's cumulative progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Cost-of-capital glide fraction, FY2030</t>
+        </is>
+      </c>
+      <c r="B120" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>the central bank's own easing calendar: the policy path's cumulative progress</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5556,7 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="27">
         <f>DCF!B32</f>
         <v/>
       </c>
@@ -5431,7 +5586,7 @@
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B9" s="26">
+      <c r="B9" s="27">
         <f>DCF!B37</f>
         <v/>
       </c>
@@ -5490,7 +5645,7 @@
           <t>Upside / (downside) to the cash-flow lens</t>
         </is>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="11">
         <f>C9/C12-1</f>
         <v/>
       </c>
@@ -5632,27 +5787,27 @@
           <t>Kiln utilisation</t>
         </is>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="12">
         <f>Assumptions!$B$28</f>
         <v/>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="12">
         <f>Assumptions!$C$28</f>
         <v/>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="12">
         <f>Assumptions!$D$28</f>
         <v/>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="12">
         <f>Assumptions!$E$28</f>
         <v/>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="12">
         <f>Assumptions!$F$28</f>
         <v/>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="12">
         <f>Assumptions!$G$28</f>
         <v/>
       </c>
@@ -5663,27 +5818,27 @@
           <t>Clinker produced (Mt)</t>
         </is>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="28">
         <f>B5*B6</f>
         <v/>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="28">
         <f>C5*C6</f>
         <v/>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="28">
         <f>D5*D6</f>
         <v/>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="28">
         <f>E5*E6</f>
         <v/>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="28">
         <f>F5*F6</f>
         <v/>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="28">
         <f>G5*G6</f>
         <v/>
       </c>
@@ -5725,27 +5880,27 @@
           <t>Clinker factor (t clinker / t cement)</t>
         </is>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="29">
         <f>Assumptions!$B$14</f>
         <v/>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="29">
         <f>Assumptions!$B$14</f>
         <v/>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="29">
         <f>Assumptions!$B$14</f>
         <v/>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="29">
         <f>Assumptions!$B$14</f>
         <v/>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="29">
         <f>Assumptions!$B$14</f>
         <v/>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="29">
         <f>Assumptions!$B$14</f>
         <v/>
       </c>
@@ -5756,27 +5911,27 @@
           <t>Cement produced (Mt)</t>
         </is>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="28">
         <f>B7/B9</f>
         <v/>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="28">
         <f>C7/C9</f>
         <v/>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="28">
         <f>D7/D9</f>
         <v/>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="28">
         <f>E7/E9</f>
         <v/>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="28">
         <f>F7/F9</f>
         <v/>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="28">
         <f>G7/G9</f>
         <v/>
       </c>
@@ -5787,27 +5942,27 @@
           <t>Domestic share</t>
         </is>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="12">
         <f>Assumptions!$B$29</f>
         <v/>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="12">
         <f>Assumptions!$C$29</f>
         <v/>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="12">
         <f>Assumptions!$D$29</f>
         <v/>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="12">
         <f>Assumptions!$E$29</f>
         <v/>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="12">
         <f>Assumptions!$F$29</f>
         <v/>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="12">
         <f>Assumptions!$G$29</f>
         <v/>
       </c>
@@ -5818,27 +5973,27 @@
           <t>Domestic volume (Mt)</t>
         </is>
       </c>
-      <c r="B12" s="27">
+      <c r="B12" s="28">
         <f>B10*B11</f>
         <v/>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="28">
         <f>C10*C11</f>
         <v/>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="28">
         <f>D10*D11</f>
         <v/>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="28">
         <f>E10*E11</f>
         <v/>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="28">
         <f>F10*F11</f>
         <v/>
       </c>
-      <c r="G12" s="27">
+      <c r="G12" s="28">
         <f>G10*G11</f>
         <v/>
       </c>
@@ -5849,27 +6004,27 @@
           <t>Export volume (Mt)</t>
         </is>
       </c>
-      <c r="B13" s="27">
+      <c r="B13" s="28">
         <f>B10-B12</f>
         <v/>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="28">
         <f>C10-C12</f>
         <v/>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="28">
         <f>D10-D12</f>
         <v/>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="28">
         <f>E10-E12</f>
         <v/>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="28">
         <f>F10-F12</f>
         <v/>
       </c>
-      <c r="G13" s="27">
+      <c r="G13" s="28">
         <f>G10-G12</f>
         <v/>
       </c>
@@ -5911,27 +6066,27 @@
           <t>Export price (USD/t)</t>
         </is>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="30">
         <f>Assumptions!$B$31</f>
         <v/>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <f>Assumptions!$C$31</f>
         <v/>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <f>Assumptions!$D$31</f>
         <v/>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <f>Assumptions!$E$31</f>
         <v/>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <f>Assumptions!$F$31</f>
         <v/>
       </c>
-      <c r="G15" s="29">
+      <c r="G15" s="30">
         <f>Assumptions!$G$31</f>
         <v/>
       </c>
@@ -5942,27 +6097,27 @@
           <t>USD/EGP</t>
         </is>
       </c>
-      <c r="B16" s="29">
+      <c r="B16" s="30">
         <f>Assumptions!$B$32</f>
         <v/>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="30">
         <f>Assumptions!$C$32</f>
         <v/>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="30">
         <f>Assumptions!$D$32</f>
         <v/>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="30">
         <f>Assumptions!$E$32</f>
         <v/>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="30">
         <f>Assumptions!$F$32</f>
         <v/>
       </c>
-      <c r="G16" s="29">
+      <c r="G16" s="30">
         <f>Assumptions!$G$32</f>
         <v/>
       </c>
@@ -5973,27 +6128,27 @@
           <t>Domestic revenue (EGP mn)</t>
         </is>
       </c>
-      <c r="B17" s="30">
+      <c r="B17" s="31">
         <f>B12*B14</f>
         <v/>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="31">
         <f>C12*C14</f>
         <v/>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="31">
         <f>D12*D14</f>
         <v/>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="31">
         <f>E12*E14</f>
         <v/>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="31">
         <f>F12*F14</f>
         <v/>
       </c>
-      <c r="G17" s="30">
+      <c r="G17" s="31">
         <f>G12*G14</f>
         <v/>
       </c>
@@ -6004,27 +6159,27 @@
           <t>Export revenue (EGP mn)</t>
         </is>
       </c>
-      <c r="B18" s="30">
+      <c r="B18" s="31">
         <f>B13*B15*B16</f>
         <v/>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="31">
         <f>C13*C15*C16</f>
         <v/>
       </c>
-      <c r="D18" s="30">
+      <c r="D18" s="31">
         <f>D13*D15*D16</f>
         <v/>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="31">
         <f>E13*E15*E16</f>
         <v/>
       </c>
-      <c r="F18" s="30">
+      <c r="F18" s="31">
         <f>F13*F15*F16</f>
         <v/>
       </c>
-      <c r="G18" s="30">
+      <c r="G18" s="31">
         <f>G13*G15*G16</f>
         <v/>
       </c>
@@ -6035,27 +6190,27 @@
           <t>REVENUE (EGP mn)</t>
         </is>
       </c>
-      <c r="B19" s="31">
+      <c r="B19" s="32">
         <f>B17+B18</f>
         <v/>
       </c>
-      <c r="C19" s="31">
+      <c r="C19" s="32">
         <f>C17+C18</f>
         <v/>
       </c>
-      <c r="D19" s="31">
+      <c r="D19" s="32">
         <f>D17+D18</f>
         <v/>
       </c>
-      <c r="E19" s="31">
+      <c r="E19" s="32">
         <f>E17+E18</f>
         <v/>
       </c>
-      <c r="F19" s="31">
+      <c r="F19" s="32">
         <f>F17+F18</f>
         <v/>
       </c>
-      <c r="G19" s="31">
+      <c r="G19" s="32">
         <f>G17+G18</f>
         <v/>
       </c>
@@ -6066,27 +6221,27 @@
           <t>Blended realised price (EGP/t)</t>
         </is>
       </c>
-      <c r="B20" s="30">
+      <c r="B20" s="31">
         <f>B19/B10</f>
         <v/>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="31">
         <f>C19/C10</f>
         <v/>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="31">
         <f>D19/D10</f>
         <v/>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="31">
         <f>E19/E10</f>
         <v/>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="31">
         <f>F19/F10</f>
         <v/>
       </c>
-      <c r="G20" s="30">
+      <c r="G20" s="31">
         <f>G19/G10</f>
         <v/>
       </c>
@@ -6113,27 +6268,27 @@
           <t>Materials, fuel, power and packing (note 24)</t>
         </is>
       </c>
-      <c r="B23" s="30">
+      <c r="B23" s="31">
         <f>Assumptions!$B$16/$B$10*(Assumptions!$B$19*B16/Assumptions!$B$32+(1-Assumptions!$B$19)*Assumptions!$B$33/Assumptions!$B$33)</f>
         <v/>
       </c>
-      <c r="C23" s="30">
+      <c r="C23" s="31">
         <f>Assumptions!$B$16/$B$10*(Assumptions!$B$19*C16/Assumptions!$B$32+(1-Assumptions!$B$19)*Assumptions!$C$33/Assumptions!$B$33)</f>
         <v/>
       </c>
-      <c r="D23" s="30">
+      <c r="D23" s="31">
         <f>Assumptions!$B$16/$B$10*(Assumptions!$B$19*D16/Assumptions!$B$32+(1-Assumptions!$B$19)*Assumptions!$D$33/Assumptions!$B$33)</f>
         <v/>
       </c>
-      <c r="E23" s="30">
+      <c r="E23" s="31">
         <f>Assumptions!$B$16/$B$10*(Assumptions!$B$19*E16/Assumptions!$B$32+(1-Assumptions!$B$19)*Assumptions!$E$33/Assumptions!$B$33)</f>
         <v/>
       </c>
-      <c r="F23" s="30">
+      <c r="F23" s="31">
         <f>Assumptions!$B$16/$B$10*(Assumptions!$B$19*F16/Assumptions!$B$32+(1-Assumptions!$B$19)*Assumptions!$F$33/Assumptions!$B$33)</f>
         <v/>
       </c>
-      <c r="G23" s="30">
+      <c r="G23" s="31">
         <f>Assumptions!$B$16/$B$10*(Assumptions!$B$19*G16/Assumptions!$B$32+(1-Assumptions!$B$19)*Assumptions!$G$33/Assumptions!$B$33)</f>
         <v/>
       </c>
@@ -6144,27 +6299,27 @@
           <t>Transport, loading and export (notes 24 and 25)</t>
         </is>
       </c>
-      <c r="B24" s="30">
+      <c r="B24" s="31">
         <f>Assumptions!$B$17/$B$10*Assumptions!$B$33/Assumptions!$B$33</f>
         <v/>
       </c>
-      <c r="C24" s="30">
+      <c r="C24" s="31">
         <f>Assumptions!$B$17/$B$10*Assumptions!$C$33/Assumptions!$B$33</f>
         <v/>
       </c>
-      <c r="D24" s="30">
+      <c r="D24" s="31">
         <f>Assumptions!$B$17/$B$10*Assumptions!$D$33/Assumptions!$B$33</f>
         <v/>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="31">
         <f>Assumptions!$B$17/$B$10*Assumptions!$E$33/Assumptions!$B$33</f>
         <v/>
       </c>
-      <c r="F24" s="30">
+      <c r="F24" s="31">
         <f>Assumptions!$B$17/$B$10*Assumptions!$F$33/Assumptions!$B$33</f>
         <v/>
       </c>
-      <c r="G24" s="30">
+      <c r="G24" s="31">
         <f>Assumptions!$B$17/$B$10*Assumptions!$G$33/Assumptions!$B$33</f>
         <v/>
       </c>
@@ -6175,27 +6330,27 @@
           <t>TOTAL VARIABLE (EGP/t)</t>
         </is>
       </c>
-      <c r="B28" s="31">
+      <c r="B28" s="32">
         <f>B23+B24</f>
         <v/>
       </c>
-      <c r="C28" s="31">
+      <c r="C28" s="32">
         <f>C23+C24</f>
         <v/>
       </c>
-      <c r="D28" s="31">
+      <c r="D28" s="32">
         <f>D23+D24</f>
         <v/>
       </c>
-      <c r="E28" s="31">
+      <c r="E28" s="32">
         <f>E23+E24</f>
         <v/>
       </c>
-      <c r="F28" s="31">
+      <c r="F28" s="32">
         <f>F23+F24</f>
         <v/>
       </c>
-      <c r="G28" s="31">
+      <c r="G28" s="32">
         <f>G23+G24</f>
         <v/>
       </c>
@@ -6253,27 +6408,27 @@
           <t>Variable cost</t>
         </is>
       </c>
-      <c r="B32" s="30">
+      <c r="B32" s="31">
         <f>B28*B10</f>
         <v/>
       </c>
-      <c r="C32" s="30">
+      <c r="C32" s="31">
         <f>C28*C10</f>
         <v/>
       </c>
-      <c r="D32" s="30">
+      <c r="D32" s="31">
         <f>D28*D10</f>
         <v/>
       </c>
-      <c r="E32" s="30">
+      <c r="E32" s="31">
         <f>E28*E10</f>
         <v/>
       </c>
-      <c r="F32" s="30">
+      <c r="F32" s="31">
         <f>F28*F10</f>
         <v/>
       </c>
-      <c r="G32" s="30">
+      <c r="G32" s="31">
         <f>G28*G10</f>
         <v/>
       </c>
@@ -6284,27 +6439,27 @@
           <t>Fixed cost</t>
         </is>
       </c>
-      <c r="B33" s="30">
+      <c r="B33" s="31">
         <f>Assumptions!$B$18*Assumptions!$B$33/Assumptions!$B$33</f>
         <v/>
       </c>
-      <c r="C33" s="30">
+      <c r="C33" s="31">
         <f>Assumptions!$B$18*Assumptions!$C$33/Assumptions!$B$33</f>
         <v/>
       </c>
-      <c r="D33" s="30">
+      <c r="D33" s="31">
         <f>Assumptions!$B$18*Assumptions!$D$33/Assumptions!$B$33</f>
         <v/>
       </c>
-      <c r="E33" s="30">
+      <c r="E33" s="31">
         <f>Assumptions!$B$18*Assumptions!$E$33/Assumptions!$B$33</f>
         <v/>
       </c>
-      <c r="F33" s="30">
+      <c r="F33" s="31">
         <f>Assumptions!$B$18*Assumptions!$F$33/Assumptions!$B$33</f>
         <v/>
       </c>
-      <c r="G33" s="30">
+      <c r="G33" s="31">
         <f>Assumptions!$B$18*Assumptions!$G$33/Assumptions!$B$33</f>
         <v/>
       </c>
@@ -6315,27 +6470,27 @@
           <t>EBITDA  (AN OUTPUT)</t>
         </is>
       </c>
-      <c r="B34" s="31">
+      <c r="B34" s="32">
         <f>B31-B32-B33</f>
         <v/>
       </c>
-      <c r="C34" s="31">
+      <c r="C34" s="32">
         <f>C31-C32-C33</f>
         <v/>
       </c>
-      <c r="D34" s="31">
+      <c r="D34" s="32">
         <f>D31-D32-D33</f>
         <v/>
       </c>
-      <c r="E34" s="31">
+      <c r="E34" s="32">
         <f>E31-E32-E33</f>
         <v/>
       </c>
-      <c r="F34" s="31">
+      <c r="F34" s="32">
         <f>F31-F32-F33</f>
         <v/>
       </c>
-      <c r="G34" s="31">
+      <c r="G34" s="32">
         <f>G31-G32-G33</f>
         <v/>
       </c>
@@ -6346,27 +6501,27 @@
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="B35" s="12">
+      <c r="B35" s="11">
         <f>B34/B31</f>
         <v/>
       </c>
-      <c r="C35" s="12">
+      <c r="C35" s="11">
         <f>C34/C31</f>
         <v/>
       </c>
-      <c r="D35" s="12">
+      <c r="D35" s="11">
         <f>D34/D31</f>
         <v/>
       </c>
-      <c r="E35" s="12">
+      <c r="E35" s="11">
         <f>E34/E31</f>
         <v/>
       </c>
-      <c r="F35" s="12">
+      <c r="F35" s="11">
         <f>F34/F31</f>
         <v/>
       </c>
-      <c r="G35" s="12">
+      <c r="G35" s="11">
         <f>G34/G31</f>
         <v/>
       </c>
@@ -6377,27 +6532,27 @@
           <t>EBITDA per tonne (EGP)</t>
         </is>
       </c>
-      <c r="B36" s="30">
+      <c r="B36" s="31">
         <f>B34/B10</f>
         <v/>
       </c>
-      <c r="C36" s="30">
+      <c r="C36" s="31">
         <f>C34/C10</f>
         <v/>
       </c>
-      <c r="D36" s="30">
+      <c r="D36" s="31">
         <f>D34/D10</f>
         <v/>
       </c>
-      <c r="E36" s="30">
+      <c r="E36" s="31">
         <f>E34/E10</f>
         <v/>
       </c>
-      <c r="F36" s="30">
+      <c r="F36" s="31">
         <f>F34/F10</f>
         <v/>
       </c>
-      <c r="G36" s="30">
+      <c r="G36" s="31">
         <f>G34/G10</f>
         <v/>
       </c>
@@ -6424,7 +6579,7 @@
           <t>Bottom-up FY2025 revenue</t>
         </is>
       </c>
-      <c r="B39" s="30">
+      <c r="B39" s="31">
         <f>B19</f>
         <v/>
       </c>
@@ -6446,7 +6601,7 @@
           <t>Difference</t>
         </is>
       </c>
-      <c r="B41" s="12">
+      <c r="B41" s="11">
         <f>B39/B40-1</f>
         <v/>
       </c>
@@ -6457,7 +6612,7 @@
           <t>Bottom-up FY2025 EBITDA</t>
         </is>
       </c>
-      <c r="B42" s="30">
+      <c r="B42" s="31">
         <f>B34</f>
         <v/>
       </c>
@@ -6479,7 +6634,7 @@
           <t>Difference</t>
         </is>
       </c>
-      <c r="B44" s="12">
+      <c r="B44" s="11">
         <f>B42/B43-1</f>
         <v/>
       </c>
@@ -6570,7 +6725,7 @@
           <t>FY2025 revenue (disclosed)</t>
         </is>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="31">
         <f>Assumptions!$B$64</f>
         <v/>
       </c>
@@ -6581,7 +6736,7 @@
           <t>Normalised revenue haircut</t>
         </is>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="11">
         <f>Assumptions!$B$85</f>
         <v/>
       </c>
@@ -6592,7 +6747,7 @@
           <t>Normalised revenue base</t>
         </is>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <f>B5*B6</f>
         <v/>
       </c>
@@ -6603,7 +6758,7 @@
           <t>Mid-cycle EBITDA margin</t>
         </is>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="11">
         <f>Assumptions!$B$84</f>
         <v/>
       </c>
@@ -6614,7 +6769,7 @@
           <t>Normalised EBITDA</t>
         </is>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="31">
         <f>B7*B8</f>
         <v/>
       </c>
@@ -6625,7 +6780,7 @@
           <t>Justified EV/EBITDA</t>
         </is>
       </c>
-      <c r="B10" s="32">
+      <c r="B10" s="33">
         <f>Assumptions!$B$82</f>
         <v/>
       </c>
@@ -6636,7 +6791,7 @@
           <t>Implied enterprise value</t>
         </is>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="31">
         <f>B9*B10</f>
         <v/>
       </c>
@@ -6647,7 +6802,7 @@
           <t>Plus net cash</t>
         </is>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="31">
         <f>DCF!B36</f>
         <v/>
       </c>
@@ -6658,7 +6813,7 @@
           <t>Less non-controlling interests</t>
         </is>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="31">
         <f>-Assumptions!$B$61</f>
         <v/>
       </c>
@@ -6669,7 +6824,7 @@
           <t>Implied equity value</t>
         </is>
       </c>
-      <c r="B14" s="30">
+      <c r="B14" s="31">
         <f>B11+B12+B13</f>
         <v/>
       </c>
@@ -6688,7 +6843,7 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>NORMALISED EARNINGS POWER</t>
+          <t>NORMALISED EARNINGS POWER — RETIRED AS A LENS FOR THIS CLASS, SHOWN FOR THE RECORD</t>
         </is>
       </c>
       <c r="B17" s="10" t="n"/>
@@ -6703,7 +6858,7 @@
           <t>Normalised EBITDA</t>
         </is>
       </c>
-      <c r="B18" s="30">
+      <c r="B18" s="31">
         <f>B9</f>
         <v/>
       </c>
@@ -6714,7 +6869,7 @@
           <t>Less D&amp;A (FY2025)</t>
         </is>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="31">
         <f>-'Income Statement'!D8</f>
         <v/>
       </c>
@@ -6725,7 +6880,7 @@
           <t>Normalised EBIT</t>
         </is>
       </c>
-      <c r="B20" s="30">
+      <c r="B20" s="31">
         <f>B18+B19</f>
         <v/>
       </c>
@@ -6736,7 +6891,7 @@
           <t>Normalised NOPAT</t>
         </is>
       </c>
-      <c r="B21" s="30">
+      <c r="B21" s="31">
         <f>B20*(1-Assumptions!$B$7)</f>
         <v/>
       </c>
@@ -6747,7 +6902,7 @@
           <t>Justified price/earnings</t>
         </is>
       </c>
-      <c r="B22" s="32">
+      <c r="B22" s="33">
         <f>Assumptions!$B$83</f>
         <v/>
       </c>
@@ -6758,7 +6913,7 @@
           <t>Operating equity value</t>
         </is>
       </c>
-      <c r="B23" s="30">
+      <c r="B23" s="31">
         <f>B21*B22</f>
         <v/>
       </c>
@@ -6769,7 +6924,7 @@
           <t>Plus net cash AT FACE (not capitalised)</t>
         </is>
       </c>
-      <c r="B24" s="30">
+      <c r="B24" s="31">
         <f>DCF!B36</f>
         <v/>
       </c>
@@ -6780,7 +6935,7 @@
           <t>Less non-controlling interests</t>
         </is>
       </c>
-      <c r="B25" s="30">
+      <c r="B25" s="31">
         <f>-Assumptions!$B$61</f>
         <v/>
       </c>
@@ -6814,7 +6969,7 @@
           <t>Enterprise value at spot (EGP mn)</t>
         </is>
       </c>
-      <c r="B29" s="30">
+      <c r="B29" s="31">
         <f>Assumptions!$B$5*Assumptions!$B$6-DCF!B36</f>
         <v/>
       </c>
@@ -6825,7 +6980,7 @@
           <t>Capacity (annual tonnes)</t>
         </is>
       </c>
-      <c r="B30" s="30">
+      <c r="B30" s="31">
         <f>Assumptions!$B$12*1000000</f>
         <v/>
       </c>
@@ -6836,7 +6991,7 @@
           <t>EV per tonne at spot (USD/t)</t>
         </is>
       </c>
-      <c r="B31" s="33">
+      <c r="B31" s="34">
         <f>B29*1000000/B30/Assumptions!$B$9</f>
         <v/>
       </c>
@@ -6847,7 +7002,7 @@
           <t>Replacement cost (USD/t)</t>
         </is>
       </c>
-      <c r="B32" s="30">
+      <c r="B32" s="31">
         <f>Assumptions!$B$80</f>
         <v/>
       </c>
@@ -6858,7 +7013,7 @@
           <t>Discount to replacement cost</t>
         </is>
       </c>
-      <c r="B33" s="12">
+      <c r="B33" s="11">
         <f>B31/B32-1</f>
         <v/>
       </c>
@@ -6869,7 +7024,7 @@
           <t>Justified EV per tonne (USD/t)</t>
         </is>
       </c>
-      <c r="B34" s="30">
+      <c r="B34" s="31">
         <f>Assumptions!$B$81</f>
         <v/>
       </c>
@@ -6880,7 +7035,7 @@
           <t>Implied enterprise value (EGP mn)</t>
         </is>
       </c>
-      <c r="B35" s="30">
+      <c r="B35" s="31">
         <f>B34*B30*Assumptions!$B$9/1000000</f>
         <v/>
       </c>
@@ -6891,7 +7046,7 @@
           <t>Plus net cash</t>
         </is>
       </c>
-      <c r="B36" s="30">
+      <c r="B36" s="31">
         <f>DCF!B36</f>
         <v/>
       </c>
@@ -6902,7 +7057,7 @@
           <t>Less non-controlling interests</t>
         </is>
       </c>
-      <c r="B37" s="31">
+      <c r="B37" s="32">
         <f>-Assumptions!$B$61</f>
         <v/>
       </c>
@@ -6947,7 +7102,7 @@
           <t>Sustainable return on equity</t>
         </is>
       </c>
-      <c r="B42" s="12">
+      <c r="B42" s="11">
         <f>B21/'Balance Sheet'!D12</f>
         <v/>
       </c>
@@ -7092,23 +7247,23 @@
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="11">
         <f>B7/B5</f>
         <v/>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="11">
         <f>C7/C5</f>
         <v/>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="11">
         <f>D7/D5</f>
         <v/>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="11">
         <f>E7/E5</f>
         <v/>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="11">
         <f>F7/F5</f>
         <v/>
       </c>
@@ -7146,23 +7301,23 @@
           <t>Depreciation &amp; amortisation</t>
         </is>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="31">
         <f>B21*Assumptions!$B$21</f>
         <v/>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <f>C21*Assumptions!$B$21</f>
         <v/>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <f>D21*Assumptions!$B$21</f>
         <v/>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <f>E21*Assumptions!$B$21</f>
         <v/>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <f>F21*Assumptions!$B$21</f>
         <v/>
       </c>
@@ -7173,23 +7328,23 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="31">
         <f>B7-B8</f>
         <v/>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <f>C7-C8</f>
         <v/>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <f>D7-D8</f>
         <v/>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <f>E7-E8</f>
         <v/>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <f>F7-F8</f>
         <v/>
       </c>
@@ -7200,23 +7355,23 @@
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="12">
         <f>Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="12">
         <f>Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="12">
         <f>Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="12">
         <f>Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="12">
         <f>Assumptions!$B$7</f>
         <v/>
       </c>
@@ -7227,23 +7382,23 @@
           <t>NOPAT  (EBIT × (1 − t))</t>
         </is>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="31">
         <f>B9*(1-B10)</f>
         <v/>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <f>C9*(1-C10)</f>
         <v/>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <f>D9*(1-D10)</f>
         <v/>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <f>E9*(1-E10)</f>
         <v/>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <f>F9*(1-F10)</f>
         <v/>
       </c>
@@ -7254,23 +7409,23 @@
           <t>Memo: capital expenditure</t>
         </is>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="31">
         <f>B20</f>
         <v/>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <f>C20</f>
         <v/>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <f>D20</f>
         <v/>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <f>E20</f>
         <v/>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <f>F20</f>
         <v/>
       </c>
@@ -7281,23 +7436,23 @@
           <t>Memo: change in working capital</t>
         </is>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="31">
         <f>(B5-Assumptions!$B$64)*Assumptions!$B$40</f>
         <v/>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <f>(C5-B5)*Assumptions!$B$40</f>
         <v/>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <f>(D5-C5)*Assumptions!$B$40</f>
         <v/>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <f>(E5-D5)*Assumptions!$B$40</f>
         <v/>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <f>(F5-E5)*Assumptions!$B$40</f>
         <v/>
       </c>
@@ -7308,23 +7463,23 @@
           <t>Net capital charge  (capex + working capital − depreciation)</t>
         </is>
       </c>
-      <c r="B14" s="30">
+      <c r="B14" s="31">
         <f>B12+B13-B8</f>
         <v/>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="31">
         <f>C12+C13-C8</f>
         <v/>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="31">
         <f>D12+D13-D8</f>
         <v/>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <f>E12+E13-E8</f>
         <v/>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <f>F12+F13-F8</f>
         <v/>
       </c>
@@ -7335,23 +7490,23 @@
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B15" s="31">
+      <c r="B15" s="32">
         <f>(B11+B8-B12-B13)*(1-Assumptions!$B$56)</f>
         <v/>
       </c>
-      <c r="C15" s="31">
+      <c r="C15" s="32">
         <f>C11+C8-C12-C13</f>
         <v/>
       </c>
-      <c r="D15" s="31">
+      <c r="D15" s="32">
         <f>D11+D8-D12-D13</f>
         <v/>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="32">
         <f>E11+E8-E12-E13</f>
         <v/>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="32">
         <f>F11+F8-F12-F13</f>
         <v/>
       </c>
@@ -7362,24 +7517,24 @@
           <t>Glide fraction</t>
         </is>
       </c>
-      <c r="B16" s="34">
-        <f>(Assumptions!$B$38-Assumptions!$B$38)/(Assumptions!$B$38-Assumptions!$F$38)</f>
-        <v/>
-      </c>
-      <c r="C16" s="34">
-        <f>(Assumptions!$B$38-Assumptions!$C$38)/(Assumptions!$B$38-Assumptions!$F$38)</f>
-        <v/>
-      </c>
-      <c r="D16" s="34">
-        <f>(Assumptions!$B$38-Assumptions!$D$38)/(Assumptions!$B$38-Assumptions!$F$38)</f>
-        <v/>
-      </c>
-      <c r="E16" s="34">
-        <f>(Assumptions!$B$38-Assumptions!$E$38)/(Assumptions!$B$38-Assumptions!$F$38)</f>
-        <v/>
-      </c>
-      <c r="F16" s="34">
-        <f>(Assumptions!$B$38-Assumptions!$F$38)/(Assumptions!$B$38-Assumptions!$F$38)</f>
+      <c r="B16" s="35">
+        <f>Assumptions!$B$116</f>
+        <v/>
+      </c>
+      <c r="C16" s="35">
+        <f>Assumptions!$B$117</f>
+        <v/>
+      </c>
+      <c r="D16" s="35">
+        <f>Assumptions!$B$118</f>
+        <v/>
+      </c>
+      <c r="E16" s="35">
+        <f>Assumptions!$B$119</f>
+        <v/>
+      </c>
+      <c r="F16" s="35">
+        <f>Assumptions!$B$120</f>
         <v/>
       </c>
     </row>
@@ -7389,23 +7544,23 @@
           <t>Forward cost of capital</t>
         </is>
       </c>
-      <c r="B17" s="35">
+      <c r="B17" s="36">
         <f>$C$46-($C$46-$C$53)*B16</f>
         <v/>
       </c>
-      <c r="C17" s="35">
+      <c r="C17" s="36">
         <f>$C$46-($C$46-$C$53)*C16</f>
         <v/>
       </c>
-      <c r="D17" s="35">
+      <c r="D17" s="36">
         <f>$C$46-($C$46-$C$53)*D16</f>
         <v/>
       </c>
-      <c r="E17" s="35">
+      <c r="E17" s="36">
         <f>$C$46-($C$46-$C$53)*E16</f>
         <v/>
       </c>
-      <c r="F17" s="35">
+      <c r="F17" s="36">
         <f>$C$46-($C$46-$C$53)*F16</f>
         <v/>
       </c>
@@ -7416,24 +7571,24 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B18" s="34">
+      <c r="B18" s="35">
         <f>1/(1+B17)^((1-Assumptions!$B$56)/2)</f>
         <v/>
       </c>
-      <c r="C18" s="34">
-        <f>1/(1+B17)^(1-Assumptions!$B$56+0.5)</f>
-        <v/>
-      </c>
-      <c r="D18" s="34">
-        <f>1/((1+B17)*(1+C17)^(1-Assumptions!$B$56+0.5))</f>
-        <v/>
-      </c>
-      <c r="E18" s="34">
-        <f>1/((1+B17)*(1+C17)*(1+D17)^(1-Assumptions!$B$56+0.5))</f>
-        <v/>
-      </c>
-      <c r="F18" s="34">
-        <f>1/((1+B17)*(1+C17)*(1+D17)*(1+E17)^(1-Assumptions!$B$56+0.5))</f>
+      <c r="C18" s="35">
+        <f>1/((1+B17)^(1-Assumptions!$B$56)*(1+C17)^0.5)</f>
+        <v/>
+      </c>
+      <c r="D18" s="35">
+        <f>1/((1+B17)^(1-Assumptions!$B$56)*(1+C17)*(1+D17)^0.5)</f>
+        <v/>
+      </c>
+      <c r="E18" s="35">
+        <f>1/((1+B17)^(1-Assumptions!$B$56)*(1+C17)*(1+D17)*(1+E17)^0.5)</f>
+        <v/>
+      </c>
+      <c r="F18" s="35">
+        <f>1/((1+B17)^(1-Assumptions!$B$56)*(1+C17)*(1+D17)*(1+E17)*(1+F17)^0.5)</f>
         <v/>
       </c>
     </row>
@@ -7443,23 +7598,23 @@
           <t>Present value of FCFF</t>
         </is>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="31">
         <f>B15*B18</f>
         <v/>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="31">
         <f>C15*C18</f>
         <v/>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="31">
         <f>D15*D18</f>
         <v/>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="31">
         <f>E15*E18</f>
         <v/>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="31">
         <f>F15*F18</f>
         <v/>
       </c>
@@ -7470,24 +7625,24 @@
           <t>Memo: capital expenditure, on the company's own run rate</t>
         </is>
       </c>
-      <c r="B20" s="30">
-        <f>Assumptions!$B$22*Assumptions!$C$33/Assumptions!$B$33</f>
-        <v/>
-      </c>
-      <c r="C20" s="30">
-        <f>Assumptions!$B$22*Assumptions!$D$33/Assumptions!$B$33</f>
-        <v/>
-      </c>
-      <c r="D20" s="30">
-        <f>Assumptions!$B$22*Assumptions!$E$33/Assumptions!$B$33</f>
-        <v/>
-      </c>
-      <c r="E20" s="30">
-        <f>Assumptions!$B$22*Assumptions!$F$33/Assumptions!$B$33</f>
-        <v/>
-      </c>
-      <c r="F20" s="30">
-        <f>Assumptions!$B$22*Assumptions!$G$33/Assumptions!$B$33</f>
+      <c r="B20" s="31">
+        <f>(Assumptions!$B$22+(Assumptions!$B$89-Assumptions!$B$22)*Assumptions!$B$105)*Assumptions!$C$33/Assumptions!$B$33</f>
+        <v/>
+      </c>
+      <c r="C20" s="31">
+        <f>(Assumptions!$B$22+(Assumptions!$B$89-Assumptions!$B$22)*Assumptions!$B$106)*Assumptions!$D$33/Assumptions!$B$33</f>
+        <v/>
+      </c>
+      <c r="D20" s="31">
+        <f>(Assumptions!$B$22+(Assumptions!$B$89-Assumptions!$B$22)*Assumptions!$B$107)*Assumptions!$E$33/Assumptions!$B$33</f>
+        <v/>
+      </c>
+      <c r="E20" s="31">
+        <f>(Assumptions!$B$22+(Assumptions!$B$89-Assumptions!$B$22)*Assumptions!$B$108)*Assumptions!$F$33/Assumptions!$B$33</f>
+        <v/>
+      </c>
+      <c r="F20" s="31">
+        <f>(Assumptions!$B$22+(Assumptions!$B$89-Assumptions!$B$22)*Assumptions!$B$109)*Assumptions!$G$33/Assumptions!$B$33</f>
         <v/>
       </c>
     </row>
@@ -7497,23 +7652,23 @@
           <t>TERMINAL BLOCK</t>
         </is>
       </c>
-      <c r="B21" s="36">
+      <c r="B21" s="37">
         <f>Assumptions!$B$20+B20</f>
         <v/>
       </c>
-      <c r="C21" s="36">
+      <c r="C21" s="37">
         <f>B21+C20</f>
         <v/>
       </c>
-      <c r="D21" s="36">
+      <c r="D21" s="37">
         <f>C21+D20</f>
         <v/>
       </c>
-      <c r="E21" s="36">
+      <c r="E21" s="37">
         <f>D21+E20</f>
         <v/>
       </c>
-      <c r="F21" s="36">
+      <c r="F21" s="37">
         <f>E21+F20</f>
         <v/>
       </c>
@@ -7526,7 +7681,7 @@
           <t>Replacement-cost invested capital (EGP mn)</t>
         </is>
       </c>
-      <c r="B22" s="30">
+      <c r="B22" s="31">
         <f>Assumptions!$B$12*1000000*Assumptions!$B$80*Assumptions!$B$9/1000000</f>
         <v/>
       </c>
@@ -7537,7 +7692,7 @@
           <t>FY2025 NOPAT (the reinvestment base)</t>
         </is>
       </c>
-      <c r="B23" s="30">
+      <c r="B23" s="31">
         <f>('Income Statement'!D6-'Income Statement'!D8)*(1-Assumptions!$B$7)</f>
         <v/>
       </c>
@@ -7548,7 +7703,7 @@
           <t>Terminal return on invested capital</t>
         </is>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="11">
         <f>F11*(1+Assumptions!$B$55)/B22</f>
         <v/>
       </c>
@@ -7559,7 +7714,7 @@
           <t>Maintenance at current cost  (invested capital / life)</t>
         </is>
       </c>
-      <c r="B25" s="30">
+      <c r="B25" s="31">
         <f>B22/B45</f>
         <v/>
       </c>
@@ -7570,7 +7725,7 @@
           <t>Terminal value</t>
         </is>
       </c>
-      <c r="B26" s="30">
+      <c r="B26" s="31">
         <f>B48*(1+Assumptions!$B$55)/($C$53-Assumptions!$B$55)</f>
         <v/>
       </c>
@@ -7581,7 +7736,7 @@
           <t>Present value of terminal value</t>
         </is>
       </c>
-      <c r="B27" s="30">
+      <c r="B27" s="31">
         <f>B26*F18</f>
         <v/>
       </c>
@@ -7592,7 +7747,7 @@
           <t>Terminal NOPAT</t>
         </is>
       </c>
-      <c r="B28" s="30">
+      <c r="B28" s="31">
         <f>F11*(1+Assumptions!$B$55)</f>
         <v/>
       </c>
@@ -7617,7 +7772,7 @@
           <t>Present value of explicit years (FY2026E-FY2030E)</t>
         </is>
       </c>
-      <c r="B30" s="30">
+      <c r="B30" s="31">
         <f>SUM(B19:F19)</f>
         <v/>
       </c>
@@ -7628,7 +7783,7 @@
           <t>Present value of terminal value</t>
         </is>
       </c>
-      <c r="B31" s="30">
+      <c r="B31" s="31">
         <f>B27</f>
         <v/>
       </c>
@@ -7639,7 +7794,7 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="B32" s="31">
+      <c r="B32" s="32">
         <f>B30+B31</f>
         <v/>
       </c>
@@ -7661,7 +7816,7 @@
           <t>Cash, reviewed sheet at 31 March 2026</t>
         </is>
       </c>
-      <c r="B34" s="30">
+      <c r="B34" s="31">
         <f>Assumptions!$B$23+B15/(1-Assumptions!$B$56)*(Assumptions!$B$56-0.25)</f>
         <v/>
       </c>
@@ -7672,7 +7827,7 @@
           <t>Less lease liabilities (there are no bank borrowings)</t>
         </is>
       </c>
-      <c r="B35" s="30">
+      <c r="B35" s="31">
         <f>-Assumptions!$B$24</f>
         <v/>
       </c>
@@ -7683,7 +7838,7 @@
           <t>Net cash (ADDED — the company is net cash)</t>
         </is>
       </c>
-      <c r="B36" s="30">
+      <c r="B36" s="31">
         <f>B34+B35</f>
         <v/>
       </c>
@@ -7694,7 +7849,7 @@
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B37" s="31">
+      <c r="B37" s="32">
         <f>B32+B36-B40</f>
         <v/>
       </c>
@@ -7705,7 +7860,7 @@
           <t>Shares outstanding (mn)</t>
         </is>
       </c>
-      <c r="B38" s="37">
+      <c r="B38" s="38">
         <f>Assumptions!$B$6</f>
         <v/>
       </c>
@@ -7727,7 +7882,7 @@
           <t>Less non-controlling interests</t>
         </is>
       </c>
-      <c r="B40" s="30">
+      <c r="B40" s="31">
         <f>Assumptions!$B$61</f>
         <v/>
       </c>
@@ -7752,7 +7907,7 @@
           <t>Risk-free rate (observed EGP 10-year)</t>
         </is>
       </c>
-      <c r="C42" s="35">
+      <c r="C42" s="36">
         <f>Assumptions!$B$45</f>
         <v/>
       </c>
@@ -7763,7 +7918,7 @@
           <t>Less sovereign default spread</t>
         </is>
       </c>
-      <c r="C43" s="35">
+      <c r="C43" s="36">
         <f>-Assumptions!$B$46</f>
         <v/>
       </c>
@@ -7774,7 +7929,7 @@
           <t>Normalised risk-free rate</t>
         </is>
       </c>
-      <c r="C44" s="35">
+      <c r="C44" s="36">
         <f>C42+C43</f>
         <v/>
       </c>
@@ -7785,11 +7940,11 @@
           <t>Cost of equity  (rf* + β × ERP)</t>
         </is>
       </c>
-      <c r="B45" s="33">
+      <c r="B45" s="34">
         <f>1/Assumptions!$B$21</f>
         <v/>
       </c>
-      <c r="C45" s="35">
+      <c r="C45" s="36">
         <f>C44+Assumptions!$B$48*Assumptions!$B$47</f>
         <v/>
       </c>
@@ -7800,11 +7955,11 @@
           <t>WACC — explicit window</t>
         </is>
       </c>
-      <c r="B46" s="30">
+      <c r="B46" s="31">
         <f>DCF!F8*(1+Assumptions!$B$55)</f>
         <v/>
       </c>
-      <c r="C46" s="38">
+      <c r="C46" s="39">
         <f>(1-C49)*C45+C49*C48</f>
         <v/>
       </c>
@@ -7812,11 +7967,15 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Working capital charged with inflation</t>
-        </is>
-      </c>
-      <c r="B47" s="30">
+          <t>Asset beta, unlevered at the observed structure</t>
+        </is>
+      </c>
+      <c r="B47" s="31">
         <f>Assumptions!$B$64*Assumptions!$B$40*Assumptions!$B$55</f>
+        <v/>
+      </c>
+      <c r="C47" s="28">
+        <f>Assumptions!$B$48/(1+(1-Assumptions!$B$7)*C49/(1-C49))</f>
         <v/>
       </c>
     </row>
@@ -7826,11 +7985,11 @@
           <t>Cost of debt after tax</t>
         </is>
       </c>
-      <c r="B48" s="30">
+      <c r="B48" s="31">
         <f>B28+B46-B25-B47</f>
         <v/>
       </c>
-      <c r="C48" s="35">
+      <c r="C48" s="36">
         <f>Assumptions!$B$49*(1-Assumptions!$B$7)</f>
         <v/>
       </c>
@@ -7841,7 +8000,7 @@
           <t>Debt weight  D/(D+E)</t>
         </is>
       </c>
-      <c r="C49" s="39">
+      <c r="C49" s="40">
         <f>Assumptions!$B$50/(Assumptions!$B$50+C50)</f>
         <v/>
       </c>
@@ -7852,7 +8011,7 @@
           <t>Market capitalisation</t>
         </is>
       </c>
-      <c r="C50" s="30">
+      <c r="C50" s="31">
         <f>Assumptions!$B$5*Assumptions!$B$6</f>
         <v/>
       </c>
@@ -7863,7 +8022,7 @@
           <t>Terminal cost of equity  (rf_term + β_L × ERP_term)</t>
         </is>
       </c>
-      <c r="C51" s="35">
+      <c r="C51" s="36">
         <f>Assumptions!$B$51+C56*Assumptions!$B$52</f>
         <v/>
       </c>
@@ -7874,7 +8033,7 @@
           <t>Terminal cost of debt after tax</t>
         </is>
       </c>
-      <c r="C52" s="35">
+      <c r="C52" s="36">
         <f>Assumptions!$B$53*(1-Assumptions!$B$7)</f>
         <v/>
       </c>
@@ -7885,7 +8044,7 @@
           <t>WACC — terminal</t>
         </is>
       </c>
-      <c r="C53" s="38">
+      <c r="C53" s="39">
         <f>(1-Assumptions!$B$54)*C51+Assumptions!$B$54*C52</f>
         <v/>
       </c>
@@ -7896,7 +8055,7 @@
           <t>Retired construction: rf NOT netted (disclosed only)</t>
         </is>
       </c>
-      <c r="C54" s="35">
+      <c r="C54" s="36">
         <f>Assumptions!$B$45+Assumptions!$B$48*Assumptions!$B$47</f>
         <v/>
       </c>
@@ -7907,7 +8066,7 @@
           <t>Sovereign double-count removed (bp)</t>
         </is>
       </c>
-      <c r="C55" s="30">
+      <c r="C55" s="31">
         <f>(C54-C45)*10000</f>
         <v/>
       </c>
@@ -7918,22 +8077,22 @@
           <t>Terminal beta, RE-LEVERED to the terminal structure (Hamada)</t>
         </is>
       </c>
-      <c r="C56" s="27">
-        <f>Assumptions!$B$48*(1+(1-Assumptions!$B$7)*Assumptions!$B$54/(1-Assumptions!$B$54))</f>
+      <c r="C56" s="28">
+        <f>C47*(1+(1-Assumptions!$B$7)*Assumptions!$B$54/(1-Assumptions!$B$54))</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>The glide fraction on row 16 is derived from the cost-of-debt path on Assumptions, so the shape of</t>
+          <t>The glide fraction on row 16 is the central bank's own easing calendar — the policy path's</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>the discount schedule is INHERITED rather than invented. The terminal value is capitalised at the</t>
+          <t>cumulative progress — so the schedule is INHERITED rather than invented. The terminal is capitalised at the</t>
         </is>
       </c>
     </row>
@@ -8102,15 +8261,15 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="31">
         <f>B9+B8</f>
         <v/>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <f>C9+C8</f>
         <v/>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <f>D9+D8</f>
         <v/>
       </c>
@@ -8141,35 +8300,35 @@
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="11">
         <f>B6/B5</f>
         <v/>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="11">
         <f>C6/C5</f>
         <v/>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="11">
         <f>D6/D5</f>
         <v/>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="11">
         <f>E6/E5</f>
         <v/>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="11">
         <f>F6/F5</f>
         <v/>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="11">
         <f>G6/G5</f>
         <v/>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="11">
         <f>H6/H5</f>
         <v/>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="11">
         <f>I6/I5</f>
         <v/>
       </c>
@@ -8231,23 +8390,23 @@
         <f>Assumptions!$D$101</f>
         <v/>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <f>E6-E8</f>
         <v/>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <f>F6-F8</f>
         <v/>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="31">
         <f>G6-G8</f>
         <v/>
       </c>
-      <c r="H9" s="30">
+      <c r="H9" s="31">
         <f>H6-H8</f>
         <v/>
       </c>
-      <c r="I9" s="30">
+      <c r="I9" s="31">
         <f>I6-I8</f>
         <v/>
       </c>
@@ -8270,23 +8429,23 @@
         <f>Assumptions!$D$102</f>
         <v/>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <f>'Balance Sheet'!D7*Assumptions!$B$39</f>
         <v/>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <f>'Balance Sheet'!E7*Assumptions!$C$39</f>
         <v/>
       </c>
-      <c r="G10" s="30">
+      <c r="G10" s="31">
         <f>'Balance Sheet'!F7*Assumptions!$D$39</f>
         <v/>
       </c>
-      <c r="H10" s="30">
+      <c r="H10" s="31">
         <f>'Balance Sheet'!G7*Assumptions!$E$39</f>
         <v/>
       </c>
-      <c r="I10" s="30">
+      <c r="I10" s="31">
         <f>'Balance Sheet'!H7*Assumptions!$F$39</f>
         <v/>
       </c>
@@ -8297,7 +8456,7 @@
           <t>Gain on disposal of Sinai White stake</t>
         </is>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="31">
         <f>0</f>
         <v/>
       </c>
@@ -8305,27 +8464,27 @@
         <f>Assumptions!$B$92</f>
         <v/>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <f>0</f>
         <v/>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <f>0</f>
         <v/>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <f>0</f>
         <v/>
       </c>
-      <c r="G11" s="30">
+      <c r="G11" s="31">
         <f>0</f>
         <v/>
       </c>
-      <c r="H11" s="30">
+      <c r="H11" s="31">
         <f>0</f>
         <v/>
       </c>
-      <c r="I11" s="30">
+      <c r="I11" s="31">
         <f>0</f>
         <v/>
       </c>
@@ -8336,35 +8495,35 @@
           <t>Profit before tax</t>
         </is>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="31">
         <f>B9+B10+B11</f>
         <v/>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <f>C9+C10+C11</f>
         <v/>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <f>D9+D10+D11</f>
         <v/>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <f>E9+E10+E11</f>
         <v/>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <f>F9+F10+F11</f>
         <v/>
       </c>
-      <c r="G12" s="30">
+      <c r="G12" s="31">
         <f>G9+G10+G11</f>
         <v/>
       </c>
-      <c r="H12" s="30">
+      <c r="H12" s="31">
         <f>H9+H10+H11</f>
         <v/>
       </c>
-      <c r="I12" s="30">
+      <c r="I12" s="31">
         <f>I9+I10+I11</f>
         <v/>
       </c>
@@ -8375,35 +8534,35 @@
           <t>Tax</t>
         </is>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="31">
         <f>B12-B14</f>
         <v/>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <f>C12-C14</f>
         <v/>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <f>D12-D14</f>
         <v/>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <f>E12*Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <f>F12*Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="31">
         <f>G12*Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="H13" s="30">
+      <c r="H13" s="31">
         <f>H12*Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I13" s="30">
+      <c r="I13" s="31">
         <f>I12*Assumptions!$B$7</f>
         <v/>
       </c>
@@ -8414,35 +8573,35 @@
           <t>Profit after tax</t>
         </is>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="27">
         <f>Assumptions!$B$65</f>
         <v/>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="27">
         <f>Assumptions!$B$66</f>
         <v/>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="27">
         <f>Assumptions!$B$67</f>
         <v/>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="32">
         <f>E12-E13</f>
         <v/>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="32">
         <f>F12-F13</f>
         <v/>
       </c>
-      <c r="G14" s="31">
+      <c r="G14" s="32">
         <f>G12-G13</f>
         <v/>
       </c>
-      <c r="H14" s="31">
+      <c r="H14" s="32">
         <f>H12-H13</f>
         <v/>
       </c>
-      <c r="I14" s="31">
+      <c r="I14" s="32">
         <f>I12-I13</f>
         <v/>
       </c>

--- a/engine/scem_study/SCEM_Valuation_Model_04092026_public.xlsx
+++ b/engine/scem_study/SCEM_Valuation_Model_04092026_public.xlsx
@@ -2179,7 +2179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -2404,96 +2404,70 @@
     <row r="13">
       <c r="A13" s="42" t="inlineStr">
         <is>
-          <t>Market panel verdict (Egypt)</t>
+          <t>Resolved three-month forecasts scored</t>
         </is>
       </c>
       <c r="B13" s="43" t="inlineStr">
         <is>
-          <t>PASS — skill +0.0158, 90% interval [0.009, 0.022]</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="42" t="inlineStr">
         <is>
-          <t>This name's verdict</t>
+          <t>Coverage 50 / 80 / 90</t>
         </is>
       </c>
       <c r="B14" s="43" t="inlineStr">
         <is>
-          <t>PARITY at every bootstrap block size {2,3,4}</t>
+          <t>0.76 / 0.82 / 0.94 against nominal 0.50 / 0.80 / 0.90 — the bands ran WIDE</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="42" t="inlineStr">
         <is>
-          <t>This name's CRPS skill vs a random walk</t>
+          <t>Cone width versus a naive carry-anchored band</t>
         </is>
       </c>
       <c r="B15" s="43" t="inlineStr">
         <is>
-          <t>-0.1276 — BELOW zero</t>
+          <t>4.64x — and this is the figure that carries the caveat below, not a score</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="42" t="inlineStr">
         <is>
-          <t>Coverage 50 / 80 / 90</t>
+          <t>Why</t>
         </is>
       </c>
       <c r="B16" s="43" t="inlineStr">
         <is>
-          <t>0.76 / 0.82 / 0.94 against nominal 0.50 / 0.80 / 0.90 — OVER-COVERED</t>
+          <t>SCEM prints an unchanged close on 29.3% of sessions, 3.4x the Egyptian panel median and 2nd thinnest of 33 names. On such a series the benchmark's own volatility estimate collapses in quiet quarters.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="42" t="inlineStr">
         <is>
-          <t>Cone width versus the benchmark</t>
+          <t>Consequence</t>
         </is>
       </c>
       <c r="B17" s="43" t="inlineStr">
         <is>
-          <t>4.71x</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="42" t="inlineStr">
-        <is>
-          <t>Why</t>
-        </is>
-      </c>
-      <c r="B18" s="43" t="inlineStr">
-        <is>
-          <t>SCEM prints an unchanged close on 29.3% of sessions, 3.4x the Egyptian panel median and 2nd thinnest of 33 names. On such a series the benchmark's own volatility estimate collapses in quiet quarters.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="42" t="inlineStr">
-        <is>
-          <t>Consequence</t>
-        </is>
-      </c>
-      <c r="B19" s="43" t="inlineStr">
-        <is>
           <t>The map is ILLUSTRATIVE ONLY. It is materially too wide and must not be read with the confidence of a calibrated name.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="5">
     <mergeCell ref="B14:H14"/>
     <mergeCell ref="B17:H17"/>
-    <mergeCell ref="B18:H18"/>
     <mergeCell ref="B13:H13"/>
     <mergeCell ref="B16:H16"/>
     <mergeCell ref="B15:H15"/>
-    <mergeCell ref="B19:H19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
